--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2022/KENTUCKY_2022.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2022/KENTUCKY_2022.xlsx
@@ -1932,7 +1932,7 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Cuatro Cienegas</t>
+          <t>Cuatrocienegas</t>
         </is>
       </c>
       <c r="C88">
@@ -3534,7 +3534,7 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Allende</t>
+          <t>San Miguel De Allende</t>
         </is>
       </c>
       <c r="C177">
@@ -3624,7 +3624,7 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Dolores Hidalgo Cuna De La Independencia Nacional</t>
+          <t>Dolores Hidalgo</t>
         </is>
       </c>
       <c r="C182">
@@ -8160,7 +8160,7 @@
       </c>
       <c r="B434" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 22 -</t>
+          <t>San Pedro Mixtepec -Dto. 22 -</t>
         </is>
       </c>
       <c r="C434">
@@ -12937,7 +12937,7 @@
         <v>25</v>
       </c>
       <c r="D699">
-        <v>0.009502090459901177</v>
+        <v>0.009502090459901176</v>
       </c>
     </row>
     <row r="700">
